--- a/sheets/국악이꽃피는나무/검수/흥타령-창밖에 (5관).xlsx
+++ b/sheets/국악이꽃피는나무/검수/흥타령-창밖에 (5관).xlsx
@@ -2915,7 +2915,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
@@ -2936,7 +2936,7 @@
       <c r="F5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">淋▾
-汰j</t>
+汰</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
@@ -3035,7 +3035,7 @@
       <c r="H7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-汰j</t>
+汰</t>
         </is>
       </c>
       <c r="I7" s="27" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j
+          <t xml:space="preserve">汰
 林</t>
         </is>
       </c>
@@ -3133,7 +3133,7 @@
       <c r="J9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">浹▾
-汰j</t>
+汰</t>
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr">
@@ -3191,7 +3191,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
@@ -3343,7 +3343,7 @@
       <c r="E14" s="26"/>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/sheets/국악이꽃피는나무/검수/흥타령-창밖에 (5관).xlsx
+++ b/sheets/국악이꽃피는나무/검수/흥타령-창밖에 (5관).xlsx
@@ -2780,22 +2780,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="46.51" customHeight="true">
+    <row r="2" ht="43.01" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="69.11" customHeight="true">
+    <row r="3" ht="63.87" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="69.11" customHeight="true">
+    <row r="4" ht="63.87" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="69.11" customHeight="true">
+    <row r="5" ht="63.87" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="24" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="69.11" customHeight="true">
+    <row r="6" ht="63.87" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="K6" s="22"/>
     </row>
-    <row r="7" ht="69.11" customHeight="true">
+    <row r="7" ht="63.87" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" ht="69.11" customHeight="true">
+    <row r="8" ht="63.87" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="26"/>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="K8" s="26"/>
     </row>
-    <row r="9" ht="69.11" customHeight="true">
+    <row r="9" ht="63.87" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="69.11" customHeight="true">
+    <row r="10" ht="63.87" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="69.11" customHeight="true">
+    <row r="11" ht="63.87" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="24" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="69.11" customHeight="true">
+    <row r="12" ht="63.87" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="69.11" customHeight="true">
+    <row r="13" ht="63.87" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="69.11" customHeight="true">
+    <row r="14" ht="63.87" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -3372,6 +3372,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="86"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="93"/>
 </worksheet>
 </file>